--- a/Review Papers (Accepted and Indexed).xlsx
+++ b/Review Papers (Accepted and Indexed).xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\MEU NOTEBOOK\Doutorado\PPGI UFPB\2026-2\Projeto de Tese II\Submissão Revisão\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D659E1-7D42-4E69-85B0-59B7802BE918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558A3FCF-CB59-4D5F-82E4-299C83B289CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Accepted papers (124)" sheetId="2" r:id="rId1"/>
-    <sheet name="Indexed papers (1332)" sheetId="1" r:id="rId2"/>
+    <sheet name="Accepted papers (117)" sheetId="2" r:id="rId1"/>
+    <sheet name="Indexed papers (1662)" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -15393,7 +15393,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>87</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>186</v>
       </c>
@@ -17159,7 +17159,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>191</v>
       </c>
@@ -17465,7 +17465,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>209</v>
       </c>
@@ -17499,7 +17499,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>211</v>
       </c>
@@ -17550,7 +17550,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="9">
         <v>214</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>215</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>223</v>
       </c>
